--- a/notebooks/test_output/oob_vs_shap_comparison_no_load.xlsx
+++ b/notebooks/test_output/oob_vs_shap_comparison_no_load.xlsx
@@ -505,16 +505,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9784174698663071</v>
+        <v>0.959051558011515</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2214076246334311</v>
+        <v>-0.2236070381231671</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2223225513429074</v>
+        <v>0.1487019375753412</v>
       </c>
       <c r="E2" t="n">
-        <v>8.875</v>
+        <v>12.375</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -530,16 +530,16 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9948201532782767</v>
+        <v>0.9939967130123495</v>
       </c>
       <c r="J2" t="n">
-        <v>0.910190615835777</v>
+        <v>0.8570381231671553</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4750521468185642</v>
+        <v>0.478959887707936</v>
       </c>
       <c r="L2" t="n">
-        <v>2.5625</v>
+        <v>3.0625</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -665,22 +665,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2943888888888889</v>
+        <v>0.3072222222222222</v>
       </c>
       <c r="C2" t="n">
-        <v>4.218015387173851</v>
+        <v>8.366310733278151</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2429208471187541</v>
+        <v>0.2372766443288376</v>
       </c>
       <c r="E2" t="n">
-        <v>25.41568183056257</v>
+        <v>23.7406245948581</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1013742978993689</v>
+        <v>0.09746323838298192</v>
       </c>
       <c r="G2" t="n">
-        <v>11.68422402249553</v>
+        <v>26.26616581547045</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
@@ -726,22 +726,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1806666666666667</v>
+        <v>0.1781666666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>6.294998424515167</v>
+        <v>9.114027884416542</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1799622368644382</v>
+        <v>0.1673547923657692</v>
       </c>
       <c r="E3" t="n">
-        <v>19.01096116724168</v>
+        <v>21.54277468032965</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0739422150221782</v>
+        <v>0.06776654558134412</v>
       </c>
       <c r="G3" t="n">
-        <v>9.022167769594388</v>
+        <v>32.64308923675556</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
@@ -753,13 +753,13 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6137006982449518</v>
+        <v>0.5799276672694395</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7293980481677745</v>
+        <v>0.6953036519785583</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1156973499228228</v>
+        <v>0.1153759847091188</v>
       </c>
       <c r="N3" t="n">
         <v>2</v>
@@ -768,1358 +768,1358 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7408266478523435</v>
+        <v>0.7053150673095119</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.011428599684569</v>
+        <v>0.01001141533095362</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9887005373507005</v>
+        <v>0.9900878196236296</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8963004170164732</v>
+        <v>0.896558661571678</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>load_under_load</t>
+          <t>current_phase_a_current_phase_b_env_mean_mag_ratio</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04999999999999999</v>
+        <v>-0.002555555555555541</v>
       </c>
       <c r="C4" t="n">
-        <v>3.378351342122443</v>
+        <v>-0.7782068671875879</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01944866375700242</v>
+        <v>0.01592580516007391</v>
       </c>
       <c r="E4" t="n">
-        <v>7.443188598705782</v>
+        <v>8.347255679159916</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01463406787634083</v>
+        <v>0.004704945442903551</v>
       </c>
       <c r="G4" t="n">
-        <v>6.177400313597668</v>
+        <v>2.389533378256754</v>
       </c>
       <c r="H4" t="n">
+        <v>22</v>
+      </c>
+      <c r="I4" t="n">
+        <v>24</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.008318264014466498</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.04827405205248221</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.05659231606694871</v>
+      </c>
+      <c r="N4" t="n">
+        <v>27</v>
+      </c>
+      <c r="O4" t="n">
         <v>3</v>
       </c>
-      <c r="I4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.1698433666729571</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.1443567864792279</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.02548658019372924</v>
-      </c>
-      <c r="N4" t="n">
-        <v>17</v>
-      </c>
-      <c r="O4" t="n">
-        <v>13</v>
-      </c>
       <c r="P4" t="n">
-        <v>0.08006173199081081</v>
+        <v>0.06711914358499867</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.06429505448841706</v>
+        <v>0.01884509153251646</v>
       </c>
       <c r="R4" t="n">
-        <v>0.07110203505584621</v>
+        <v>0.2488277047818898</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4937085289917617</v>
+        <v>0.3271617201756052</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_spectral_corr</t>
+          <t>current_phase_a_env_centroid</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.003055555555555563</v>
+        <v>0.005333333333333343</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.3073150175088126</v>
+        <v>0.2467188645032127</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01884777550275823</v>
+        <v>0.02519383226664225</v>
       </c>
       <c r="E5" t="n">
-        <v>10.21756441076837</v>
+        <v>4.890803152637527</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004762436287053222</v>
+        <v>0.01030503404261676</v>
       </c>
       <c r="G5" t="n">
-        <v>5.326476104861868</v>
+        <v>4.231514170378326</v>
       </c>
       <c r="H5" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.01735985533453891</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.1057325224729669</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.08837266713842795</v>
+      </c>
+      <c r="N5" t="n">
+        <v>9</v>
+      </c>
+      <c r="O5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>-0.01037931685223629</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.04697873510089061</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.0573580519531269</v>
-      </c>
-      <c r="N5" t="n">
-        <v>18</v>
-      </c>
-      <c r="O5" t="n">
-        <v>3</v>
-      </c>
       <c r="P5" t="n">
-        <v>0.07758813509136298</v>
+        <v>0.1061791493971339</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03060939999047237</v>
+        <v>0.0004466269241670401</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2481014409390213</v>
+        <v>0.4998883681978425</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4860602650329449</v>
+        <v>0.2445960976204083</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>current_phase_a_kurtosis</t>
+          <t>current_phase_a_env_form_factor</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01372222222222222</v>
+        <v>-0.00316666666666665</v>
       </c>
       <c r="C6" t="n">
-        <v>0.987478038185562</v>
+        <v>-0.243545082062442</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03260563681180013</v>
+        <v>0.01894495827277523</v>
       </c>
       <c r="E6" t="n">
-        <v>5.657317386501933</v>
+        <v>8.20373603901165</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01383785538693269</v>
+        <v>0.004971491193489436</v>
       </c>
       <c r="G6" t="n">
-        <v>4.753951329722718</v>
+        <v>11.36999318271934</v>
       </c>
       <c r="H6" t="n">
+        <v>25</v>
+      </c>
+      <c r="I6" t="n">
+        <v>21</v>
+      </c>
+      <c r="J6" t="n">
         <v>4</v>
       </c>
-      <c r="I6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
       <c r="K6" t="n">
-        <v>0.04661256840913378</v>
+        <v>-0.01030741410488241</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1365026014845409</v>
+        <v>0.05100888577038611</v>
       </c>
       <c r="M6" t="n">
-        <v>0.08989003307540716</v>
+        <v>0.06131629987526852</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>0.134223296182812</v>
+        <v>0.07984333361744504</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.002279305301728929</v>
+        <v>0.02883444784705893</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4994308223393975</v>
+        <v>0.248210745054164</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4784940758478262</v>
+        <v>0.1975770611342042</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>current_phase_a_env_rms</t>
+          <t>current_phase_a_current_phase_b_env_time_corr</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001277777777777772</v>
+        <v>-0.001111111111111094</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1283014281372515</v>
+        <v>-0.1749409651055914</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02428467376910738</v>
+        <v>0.02645940428753181</v>
       </c>
       <c r="E7" t="n">
-        <v>6.994644401800977</v>
+        <v>7.59942662185889</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01008017024433067</v>
+        <v>0.007756734729212343</v>
       </c>
       <c r="G7" t="n">
-        <v>7.393788482157205</v>
+        <v>3.85257717142495</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>0.004340441592753331</v>
+        <v>-0.003616636528028877</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09943516703155811</v>
+        <v>0.07958626101394502</v>
       </c>
       <c r="M7" t="n">
-        <v>0.09509472543880478</v>
+        <v>0.08320289754197389</v>
       </c>
       <c r="N7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="P7" t="n">
-        <v>0.09996949235581905</v>
+        <v>0.1115128897847281</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0005343253242609397</v>
+        <v>0.03192662877078312</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4998664543473468</v>
+        <v>0.1422085372604073</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4773053876075012</v>
+        <v>0.1967263593754163</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>current_phase_a_env_harmonic_ratio</t>
+          <t>current_phase_a_env_peak_power_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.005277777777777775</v>
+        <v>-0.0003888888888888612</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.440382351776153</v>
+        <v>-0.0430444895973759</v>
       </c>
       <c r="D8" t="n">
-        <v>0.01332987546267843</v>
+        <v>0.01913126673949189</v>
       </c>
       <c r="E8" t="n">
-        <v>10.63225199076348</v>
+        <v>5.628275293070213</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002826320891354883</v>
+        <v>0.004790042842569371</v>
       </c>
       <c r="G8" t="n">
-        <v>8.489196724396216</v>
+        <v>2.871365336894171</v>
       </c>
       <c r="H8" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I8" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.01792791092658991</v>
+        <v>-0.001265822784810036</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02788005391820799</v>
+        <v>0.04914717509946562</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0458079648447979</v>
+        <v>0.05041299788427566</v>
       </c>
       <c r="N8" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P8" t="n">
-        <v>0.05487332857917294</v>
+        <v>0.08062852875219439</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.02699327466096496</v>
+        <v>0.03148135365272877</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3303608264911008</v>
+        <v>0.1657967489851211</v>
       </c>
       <c r="S8" t="n">
-        <v>0.328320108011457</v>
+        <v>0.1242172296331641</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_freq_cv</t>
+          <t>current_phase_a_skewness</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.004555555555555551</v>
+        <v>0.001500000000000011</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.6827162461620255</v>
+        <v>0.244186056604257</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01284801688864678</v>
+        <v>0.02238108086072104</v>
       </c>
       <c r="E9" t="n">
-        <v>7.689844564794694</v>
+        <v>7.360633860702936</v>
       </c>
       <c r="F9" t="n">
-        <v>0.004006603993138945</v>
+        <v>0.006340370161407561</v>
       </c>
       <c r="G9" t="n">
-        <v>3.406689285464507</v>
+        <v>5.605120064698832</v>
       </c>
       <c r="H9" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="I9" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.01547461785242497</v>
+        <v>0.004882459312839094</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03952287785130879</v>
+        <v>0.06505396564490365</v>
       </c>
       <c r="M9" t="n">
-        <v>0.05499749570373375</v>
+        <v>0.06017150633206456</v>
       </c>
       <c r="N9" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="O9" t="n">
         <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0528897253613063</v>
+        <v>0.09432483725496171</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01336684750999751</v>
+        <v>0.02927087161005806</v>
       </c>
       <c r="R9" t="n">
-        <v>0.199466751669424</v>
+        <v>0.1988359795144346</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3273325105524006</v>
+        <v>0.1240668389269882</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_time_corr</t>
+          <t>load_under_load</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.000888888888888889</v>
+        <v>0.0363888888888889</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.1661443684112394</v>
+        <v>1.603533373557706</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0250574055867606</v>
+        <v>0.0139273038606346</v>
       </c>
       <c r="E10" t="n">
-        <v>8.734368147955879</v>
+        <v>10.2556931004046</v>
       </c>
       <c r="F10" t="n">
-        <v>0.007177333994267826</v>
+        <v>0.007912848590283249</v>
       </c>
       <c r="G10" t="n">
-        <v>4.954241505780508</v>
+        <v>9.911309178578733</v>
       </c>
       <c r="H10" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.003019437629741461</v>
+        <v>0.1184448462929476</v>
       </c>
       <c r="L10" t="n">
-        <v>0.07080033246092163</v>
+        <v>0.08118803275538312</v>
       </c>
       <c r="M10" t="n">
-        <v>0.07381977009066309</v>
+        <v>0.03725681353756446</v>
       </c>
       <c r="N10" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="O10" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1031504948379793</v>
+        <v>0.05869648022050156</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.03235016237705762</v>
+        <v>0.02249155253488157</v>
       </c>
       <c r="R10" t="n">
-        <v>0.09967754153460098</v>
+        <v>0.05548622381567154</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3253281177154068</v>
+        <v>0.1106530466747418</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_energy_ratio</t>
+          <t>current_phase_a_env_peak_power_std</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.003944444444444438</v>
+        <v>-0.002888888888888869</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.8963654419748017</v>
+        <v>-0.1596594159679004</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01654983253962661</v>
+        <v>0.01983254991455375</v>
       </c>
       <c r="E11" t="n">
-        <v>6.29452548111436</v>
+        <v>17.00508249327528</v>
       </c>
       <c r="F11" t="n">
-        <v>0.003760556735643373</v>
+        <v>0.006353144117262085</v>
       </c>
       <c r="G11" t="n">
-        <v>3.274705066937364</v>
+        <v>9.171669640929274</v>
       </c>
       <c r="H11" t="n">
         <v>24</v>
       </c>
       <c r="I11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.01339875448197771</v>
+        <v>-0.00940325497287516</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03709576109100515</v>
+        <v>0.06518502999353866</v>
       </c>
       <c r="M11" t="n">
-        <v>0.05049451557298286</v>
+        <v>0.07458828496641381</v>
       </c>
       <c r="N11" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>0.06812849838094</v>
+        <v>0.08358407954837797</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.03103273728993484</v>
+        <v>0.01839904955483931</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1658090817211106</v>
+        <v>0.495442167504266</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1980004130123383</v>
+        <v>0.1101978369262955</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>current_phase_a_env_dom_rel_peak_power</t>
+          <t>current_phase_a_env_rms</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.003666666666666664</v>
+        <v>-0.005499999999999979</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.4106271128685529</v>
+        <v>-0.7560987473322507</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01975264299289732</v>
+        <v>0.01823599055858742</v>
       </c>
       <c r="E12" t="n">
-        <v>4.901855957905414</v>
+        <v>8.069431697029451</v>
       </c>
       <c r="F12" t="n">
-        <v>0.004942264773402912</v>
+        <v>0.00562166310619692</v>
       </c>
       <c r="G12" t="n">
-        <v>3.122608588195283</v>
+        <v>3.344582543180752</v>
       </c>
       <c r="H12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.01245518022268352</v>
+        <v>-0.01790235081374315</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04875264120999333</v>
+        <v>0.05767983087229862</v>
       </c>
       <c r="M12" t="n">
-        <v>0.06120782143267685</v>
+        <v>0.07558218168604176</v>
       </c>
       <c r="N12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>0.08131308295348176</v>
+        <v>0.0768553964094101</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.03256044174348843</v>
+        <v>0.01917556553711148</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2479814039855153</v>
+        <v>0.3312162470492503</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1975812958648534</v>
+        <v>0.1101857688003683</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>current_phase_a_env_fundamental_power_ratio</t>
+          <t>current_phase_a_current_phase_b_env_crest_diff</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-5.555555555556008e-05</v>
+        <v>-0.001333333333333315</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.005135701761997412</v>
+        <v>-0.09854448275797806</v>
       </c>
       <c r="D13" t="n">
-        <v>0.03078080624405995</v>
+        <v>0.01846416361799701</v>
       </c>
       <c r="E13" t="n">
-        <v>8.464264337520843</v>
+        <v>7.73126355811013</v>
       </c>
       <c r="F13" t="n">
-        <v>0.01283893740658587</v>
+        <v>0.003912083517319595</v>
       </c>
       <c r="G13" t="n">
-        <v>5.35120731474129</v>
+        <v>6.241155874880072</v>
       </c>
       <c r="H13" t="n">
+        <v>17</v>
+      </c>
+      <c r="I13" t="n">
+        <v>27</v>
+      </c>
+      <c r="J13" t="n">
         <v>10</v>
       </c>
-      <c r="I13" t="n">
-        <v>6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>4</v>
-      </c>
       <c r="K13" t="n">
-        <v>-0.0001887148518588566</v>
+        <v>-0.004339963833634661</v>
       </c>
       <c r="L13" t="n">
-        <v>0.126648841694871</v>
+        <v>0.04013906763437367</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1268375565467299</v>
+        <v>0.04447903146800833</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P13" t="n">
-        <v>0.126711258457832</v>
+        <v>0.07781702944352099</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.241676296100951e-05</v>
+        <v>0.03767796180914733</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4999843962962262</v>
+        <v>0.1106478903348556</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1950520157836964</v>
+        <v>0.09054297601098187</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_mean_mag_ratio</t>
+          <t>current_phase_a_env_peak_freq_cv</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.002499999999999999</v>
+        <v>-0.002833333333333317</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.3977469316059385</v>
+        <v>-0.720239452993982</v>
       </c>
       <c r="D14" t="n">
-        <v>0.01649802046618768</v>
+        <v>0.01618447763481459</v>
       </c>
       <c r="E14" t="n">
-        <v>8.592545734884725</v>
+        <v>6.838047722598232</v>
       </c>
       <c r="F14" t="n">
-        <v>0.004095223743154696</v>
+        <v>0.006752343013665267</v>
       </c>
       <c r="G14" t="n">
-        <v>5.52013674762164</v>
+        <v>4.5608746903379</v>
       </c>
       <c r="H14" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I14" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="J14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.008492168333647854</v>
+        <v>-0.009222423146473726</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04039706146443448</v>
+        <v>0.06928092197318467</v>
       </c>
       <c r="M14" t="n">
-        <v>0.04888922979808234</v>
+        <v>0.0785033451196584</v>
       </c>
       <c r="N14" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P14" t="n">
-        <v>0.06791521049703267</v>
+        <v>0.06820931609427516</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.02751814903259819</v>
+        <v>0.001071605878909504</v>
       </c>
       <c r="R14" t="n">
-        <v>0.973218819484107</v>
+        <v>0.07142310447009713</v>
       </c>
       <c r="S14" t="n">
-        <v>0.16531960861075</v>
+        <v>0.09026490030718125</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>current_phase_a_env_flatness</t>
+          <t>current_phase_a_current_phase_b_env_rms_ratio</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>-0.0008888888888888936</v>
+        <v>0.0001666666666666872</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.06600866367579465</v>
+        <v>0.01293920057068518</v>
       </c>
       <c r="D15" t="n">
-        <v>0.02390640054843028</v>
+        <v>0.01782923144659737</v>
       </c>
       <c r="E15" t="n">
-        <v>7.273418752070365</v>
+        <v>8.862581466974671</v>
       </c>
       <c r="F15" t="n">
-        <v>0.008745545480911467</v>
+        <v>0.004739664252789012</v>
       </c>
       <c r="G15" t="n">
-        <v>3.227041193405296</v>
+        <v>4.580597218583002</v>
       </c>
       <c r="H15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I15" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.003019437629741476</v>
+        <v>0.0005424954792044067</v>
       </c>
       <c r="L15" t="n">
-        <v>0.08626985007178939</v>
+        <v>0.04863027672202411</v>
       </c>
       <c r="M15" t="n">
-        <v>0.08928928770153087</v>
+        <v>0.0480877812428197</v>
       </c>
       <c r="N15" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0.09841230520962002</v>
+        <v>0.07514111427624603</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.01214245513783063</v>
+        <v>0.02651083755422193</v>
       </c>
       <c r="R15" t="n">
-        <v>0.988003215282401</v>
+        <v>0.4934589943801589</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1642227775283544</v>
+        <v>0.08300072328132099</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_power_mean</t>
+          <t>current_phase_a_current_phase_b_env_spectral_corr</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.003944444444444456</v>
+        <v>0.001833333333333352</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.6560017781888221</v>
+        <v>0.3647348030279102</v>
       </c>
       <c r="D16" t="n">
-        <v>0.01875121955325727</v>
+        <v>0.01958491819206293</v>
       </c>
       <c r="E16" t="n">
-        <v>7.055122141168508</v>
+        <v>11.92821058690153</v>
       </c>
       <c r="F16" t="n">
-        <v>0.00571279958605532</v>
+        <v>0.005389105355933278</v>
       </c>
       <c r="G16" t="n">
-        <v>3.51705200675964</v>
+        <v>4.330603938232073</v>
       </c>
       <c r="H16" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="I16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.01339875448197777</v>
+        <v>0.005967450271247801</v>
       </c>
       <c r="L16" t="n">
-        <v>0.05635353047501487</v>
+        <v>0.05529372351405749</v>
       </c>
       <c r="M16" t="n">
-        <v>0.06975228495699264</v>
+        <v>0.04932627324280969</v>
       </c>
       <c r="N16" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>0.07719065603328215</v>
+        <v>0.08254043817696838</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.02083712555826728</v>
+        <v>0.02724671466291088</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4948444322170421</v>
+        <v>0.2483086015959919</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1239195411071196</v>
+        <v>0.08299219203820862</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_power_std</t>
+          <t>current_phase_a_env_spread</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.002722222222222229</v>
+        <v>-0.00572222222222221</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.4123030692847371</v>
+        <v>-0.8341778117323647</v>
       </c>
       <c r="D17" t="n">
-        <v>0.02313694126253007</v>
+        <v>0.0179713952545013</v>
       </c>
       <c r="E17" t="n">
-        <v>4.526314476393889</v>
+        <v>6.759277022510401</v>
       </c>
       <c r="F17" t="n">
-        <v>0.007477138789804874</v>
+        <v>0.006430554335399056</v>
       </c>
       <c r="G17" t="n">
-        <v>2.339694066711908</v>
+        <v>3.470669746592865</v>
       </c>
       <c r="H17" t="n">
+        <v>27</v>
+      </c>
+      <c r="I17" t="n">
+        <v>15</v>
+      </c>
+      <c r="J17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.01862567811934896</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.06597928041473632</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.08460495853408528</v>
+      </c>
+      <c r="N17" t="n">
         <v>21</v>
       </c>
-      <c r="I17" t="n">
-        <v>14</v>
-      </c>
-      <c r="J17" t="n">
-        <v>7</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-0.009247027741083245</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.07375773686962742</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.08300476461071066</v>
-      </c>
-      <c r="N17" t="n">
-        <v>10</v>
-      </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P17" t="n">
-        <v>0.09524477432445046</v>
+        <v>0.07574026219620271</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.02148703745482304</v>
+        <v>0.009760981781466394</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1991441962392991</v>
+        <v>0.142658216535346</v>
       </c>
       <c r="S17" t="n">
-        <v>0.123716368989195</v>
+        <v>0.07642569287869685</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_energy_imbalance</t>
+          <t>current_phase_a_kurtosis</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.0008888888888888957</v>
+        <v>-0.002555555555555532</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.08835321450334323</v>
+        <v>-0.1349535894186841</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01442038117996775</v>
+        <v>0.02473580349663825</v>
       </c>
       <c r="E18" t="n">
-        <v>17.69732673716507</v>
+        <v>7.086396573568891</v>
       </c>
       <c r="F18" t="n">
-        <v>0.004131922516786376</v>
+        <v>0.009977506388510245</v>
       </c>
       <c r="G18" t="n">
-        <v>5.393882882347886</v>
+        <v>9.414988157100135</v>
       </c>
       <c r="H18" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="I18" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.003019437629741483</v>
+        <v>-0.008318264014466469</v>
       </c>
       <c r="L18" t="n">
-        <v>0.04075907406912951</v>
+        <v>0.1023719974222857</v>
       </c>
       <c r="M18" t="n">
-        <v>0.04377851169887099</v>
+        <v>0.1106902614367522</v>
       </c>
       <c r="N18" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>0.05936246868478196</v>
+        <v>0.1042487918126376</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.01860339461565245</v>
+        <v>0.001876794390351849</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1992586226424821</v>
+        <v>0.4995312412842761</v>
       </c>
       <c r="S18" t="n">
-        <v>0.110573251955078</v>
+        <v>0.07627363472550024</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>current_phase_a_env_entropy</t>
+          <t>current_phase_a_env_harmonic_ratio</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.002555555555555565</v>
+        <v>-0.001666666666666648</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.2418907105887791</v>
+        <v>-0.08535614875023992</v>
       </c>
       <c r="D19" t="n">
-        <v>0.02196361944217854</v>
+        <v>0.0235278320294488</v>
       </c>
       <c r="E19" t="n">
-        <v>14.98663367974615</v>
+        <v>7.897835427080643</v>
       </c>
       <c r="F19" t="n">
-        <v>0.007718161894265871</v>
+        <v>0.01121008202338724</v>
       </c>
       <c r="G19" t="n">
-        <v>10.67838167440326</v>
+        <v>4.9404711178212</v>
       </c>
       <c r="H19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I19" t="n">
+        <v>7</v>
+      </c>
+      <c r="J19" t="n">
         <v>12</v>
       </c>
-      <c r="J19" t="n">
-        <v>8</v>
-      </c>
       <c r="K19" t="n">
-        <v>-0.008680883185506732</v>
+        <v>-0.00542495479204334</v>
       </c>
       <c r="L19" t="n">
-        <v>0.07613529320743065</v>
+        <v>0.1150185670964185</v>
       </c>
       <c r="M19" t="n">
-        <v>0.08481617639293738</v>
+        <v>0.1204435218884619</v>
       </c>
       <c r="N19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>0.09041471616242727</v>
+        <v>0.09915780837174175</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.01427942295499662</v>
+        <v>0.01586075872467677</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4964554513161714</v>
+        <v>0.1993675757965534</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1100737737103056</v>
+        <v>0.07621693567993555</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>current_phase_a_env_form_factor</t>
+          <t>current_phase_a_env_harmonic_count</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-5.555555555556771e-05</v>
+        <v>-0.001499999999999977</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.003561130240666648</v>
+        <v>-0.1982079219680779</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0168028294032441</v>
+        <v>0.003086231173568153</v>
       </c>
       <c r="E20" t="n">
-        <v>11.37461755057005</v>
+        <v>4.68746535355074</v>
       </c>
       <c r="F20" t="n">
-        <v>0.004866278115596373</v>
+        <v>0.001204722003530526</v>
       </c>
       <c r="G20" t="n">
-        <v>3.965495152672704</v>
+        <v>2.583987771601263</v>
       </c>
       <c r="H20" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J20" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0001887148518588825</v>
+        <v>-0.004882459312838983</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04800307589234281</v>
+        <v>0.01236078365051415</v>
       </c>
       <c r="M20" t="n">
-        <v>0.04819179074420169</v>
+        <v>0.01724324296335313</v>
       </c>
       <c r="N20" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="O20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.06916997698032018</v>
+        <v>0.01300688983653612</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.02116690108797737</v>
+        <v>0.0006461061860219657</v>
       </c>
       <c r="R20" t="n">
-        <v>0.330997933162806</v>
+        <v>0.9993543109976367</v>
       </c>
       <c r="S20" t="n">
-        <v>0.09952039340263595</v>
+        <v>0.07134070392207821</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_rms_ratio</t>
+          <t>current_phase_a_form_factor</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.0004444444444444522</v>
+        <v>0.002388888888888911</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.05710492056212714</v>
+        <v>0.1375860087566095</v>
       </c>
       <c r="D21" t="n">
-        <v>0.01776123094766423</v>
+        <v>0.02312660296721494</v>
       </c>
       <c r="E21" t="n">
-        <v>9.34086303035401</v>
+        <v>7.054075718380079</v>
       </c>
       <c r="F21" t="n">
-        <v>0.004197489977556562</v>
+        <v>0.005029588275786001</v>
       </c>
       <c r="G21" t="n">
-        <v>3.358528349597385</v>
+        <v>4.42564674112387</v>
       </c>
       <c r="H21" t="n">
+        <v>7</v>
+      </c>
+      <c r="I21" t="n">
+        <v>20</v>
+      </c>
+      <c r="J21" t="n">
+        <v>13</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.007775768535262278</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.05160497803307364</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.04382920949781136</v>
+      </c>
+      <c r="N21" t="n">
         <v>12</v>
       </c>
-      <c r="I21" t="n">
-        <v>22</v>
-      </c>
-      <c r="J21" t="n">
-        <v>10</v>
-      </c>
-      <c r="K21" t="n">
-        <v>-0.001509718814870756</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.04140585991257153</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.04291557872744228</v>
-      </c>
-      <c r="N21" t="n">
-        <v>20</v>
-      </c>
       <c r="O21" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P21" t="n">
-        <v>0.0731153013762606</v>
+        <v>0.09746683257693149</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.03170944146368907</v>
+        <v>0.04586185454385786</v>
       </c>
       <c r="R21" t="n">
-        <v>0.32984691287474</v>
+        <v>0.1105477859467516</v>
       </c>
       <c r="S21" t="n">
-        <v>0.09055579505890214</v>
+        <v>0.0712056509006605</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_sp_std</t>
+          <t>current_phase_a_current_phase_b_env_energy_ratio</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.001833333333333337</v>
+        <v>0.000444444444444464</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.2288355498150881</v>
+        <v>0.03514791868070168</v>
       </c>
       <c r="D22" t="n">
-        <v>0.01490897956567395</v>
+        <v>0.0176164035547225</v>
       </c>
       <c r="E22" t="n">
-        <v>6.952563913478636</v>
+        <v>11.5292040146167</v>
       </c>
       <c r="F22" t="n">
-        <v>0.00389347446250036</v>
+        <v>0.004613736971802689</v>
       </c>
       <c r="G22" t="n">
-        <v>7.514988798193675</v>
+        <v>3.197189646235021</v>
       </c>
       <c r="H22" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.006227590111341776</v>
+        <v>0.001446654611211637</v>
       </c>
       <c r="L22" t="n">
-        <v>0.03840691914202247</v>
+        <v>0.04733822770871828</v>
       </c>
       <c r="M22" t="n">
-        <v>0.04463450925336425</v>
+        <v>0.04589157309750664</v>
       </c>
       <c r="N22" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P22" t="n">
-        <v>0.06137381679055957</v>
+        <v>0.07424415329436398</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.02296689764853709</v>
+        <v>0.02690592558564571</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9775487381836788</v>
+        <v>0.330370359893666</v>
       </c>
       <c r="S22" t="n">
-        <v>0.09054170141729766</v>
+        <v>0.06646332622707644</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>current_phase_a_form_factor</t>
+          <t>current_phase_a_env_flatness</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.004611111111111108</v>
+        <v>-0.006833333333333318</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4125012495723909</v>
+        <v>-0.4035800821799471</v>
       </c>
       <c r="D23" t="n">
-        <v>0.02437857358797</v>
+        <v>0.02063956958477591</v>
       </c>
       <c r="E23" t="n">
-        <v>8.587039523229656</v>
+        <v>8.797854761363308</v>
       </c>
       <c r="F23" t="n">
-        <v>0.006889613841433298</v>
+        <v>0.006542128011269929</v>
       </c>
       <c r="G23" t="n">
-        <v>4.590599881644952</v>
+        <v>3.651767434212092</v>
       </c>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="I23" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J23" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K23" t="n">
-        <v>0.01566333270428382</v>
+        <v>-0.02224231464737789</v>
       </c>
       <c r="L23" t="n">
-        <v>0.06796213620411362</v>
+        <v>0.06712405743756049</v>
       </c>
       <c r="M23" t="n">
-        <v>0.05229880349982981</v>
+        <v>0.08936637208493838</v>
       </c>
       <c r="N23" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="O23" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1003560372735416</v>
+        <v>0.0869852557261046</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.03239390106942801</v>
+        <v>0.01986119828854412</v>
       </c>
       <c r="R23" t="n">
-        <v>0.09967710696580628</v>
+        <v>0.9805255868917517</v>
       </c>
       <c r="S23" t="n">
-        <v>0.08297172317944963</v>
+        <v>0.0662718351017033</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>current_phase_a_env_spread</t>
+          <t>current_phase_a_env_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.005999999999999998</v>
+        <v>-0.002111111111111092</v>
       </c>
       <c r="C24" t="n">
-        <v>-1.786155927199358</v>
+        <v>-0.1487441150871864</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01752049874580865</v>
+        <v>0.03018106316181319</v>
       </c>
       <c r="E24" t="n">
-        <v>8.354512535366464</v>
+        <v>7.477374396239294</v>
       </c>
       <c r="F24" t="n">
-        <v>0.006045428394587391</v>
+        <v>0.01225829902698312</v>
       </c>
       <c r="G24" t="n">
-        <v>7.108993756613351</v>
+        <v>8.980386206377551</v>
       </c>
       <c r="H24" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="I24" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="J24" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.02038120400075485</v>
+        <v>-0.00687160940325491</v>
       </c>
       <c r="L24" t="n">
-        <v>0.05963472517056049</v>
+        <v>0.1257735658116974</v>
       </c>
       <c r="M24" t="n">
-        <v>0.08001592917131534</v>
+        <v>0.1326451752149523</v>
       </c>
       <c r="N24" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="O24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>0.07212431108164047</v>
+        <v>0.1271977831917826</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.01248958591107998</v>
+        <v>0.001424217380085219</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1995016613721778</v>
+        <v>0.9985778081302935</v>
       </c>
       <c r="S24" t="n">
-        <v>0.076452506282487</v>
+        <v>0.061986115056713</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>current_phase_a_env_harmonic_count</t>
+          <t>current_phase_a_env_peak_sp_std</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.0023888888888889</v>
+        <v>-0.0003333333333333312</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.6456118797431364</v>
+        <v>-0.05879517639799603</v>
       </c>
       <c r="D25" t="n">
-        <v>0.003715521541090539</v>
+        <v>0.01142412690924837</v>
       </c>
       <c r="E25" t="n">
-        <v>3.284628569144682</v>
+        <v>5.034055188659786</v>
       </c>
       <c r="F25" t="n">
-        <v>0.001977357767141727</v>
+        <v>0.002606461210871256</v>
       </c>
       <c r="G25" t="n">
-        <v>2.281519600047636</v>
+        <v>2.329326738395816</v>
       </c>
       <c r="H25" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I25" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J25" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.00811473862993021</v>
+        <v>-0.001084990958408673</v>
       </c>
       <c r="L25" t="n">
-        <v>0.01950551380493494</v>
+        <v>0.02674301874342779</v>
       </c>
       <c r="M25" t="n">
-        <v>0.02762025243486515</v>
+        <v>0.02782800970183646</v>
       </c>
       <c r="N25" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>0.0152951942377929</v>
+        <v>0.04814686646282754</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.004210319567142039</v>
+        <v>0.02140384771939975</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9958073329011825</v>
+        <v>0.979044676826712</v>
       </c>
       <c r="S25" t="n">
-        <v>0.07128792924276828</v>
+        <v>0.0587273960854101</v>
       </c>
     </row>
     <row r="26">
@@ -2129,485 +2129,485 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.004222222222222222</v>
+        <v>0.001777777777777803</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.4956211437180896</v>
+        <v>0.1440242615097879</v>
       </c>
       <c r="D26" t="n">
-        <v>0.02131438867317483</v>
+        <v>0.0174121060348581</v>
       </c>
       <c r="E26" t="n">
-        <v>8.581540914369436</v>
+        <v>9.445453962873854</v>
       </c>
       <c r="F26" t="n">
-        <v>0.007682957769343565</v>
+        <v>0.004537923598071085</v>
       </c>
       <c r="G26" t="n">
-        <v>6.295439229864781</v>
+        <v>6.463175343259134</v>
       </c>
       <c r="H26" t="n">
+        <v>9</v>
+      </c>
+      <c r="I26" t="n">
         <v>26</v>
       </c>
-      <c r="I26" t="n">
-        <v>13</v>
-      </c>
       <c r="J26" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.01434232874127194</v>
+        <v>0.005786618444846374</v>
       </c>
       <c r="L26" t="n">
-        <v>0.07578802446523672</v>
+        <v>0.04656036135634349</v>
       </c>
       <c r="M26" t="n">
-        <v>0.09013035320650865</v>
+        <v>0.04077374291149712</v>
       </c>
       <c r="N26" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="O26" t="n">
         <v>2</v>
       </c>
       <c r="P26" t="n">
-        <v>0.08774211405065242</v>
+        <v>0.07338314347840724</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.0119540895854157</v>
+        <v>0.02682278212206375</v>
       </c>
       <c r="R26" t="n">
-        <v>0.3320103727536054</v>
+        <v>0.3303794348009083</v>
       </c>
       <c r="S26" t="n">
-        <v>0.07097166420269695</v>
+        <v>0.05542999509058838</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>current_phase_a_env_thd_power_frac</t>
+          <t>frequency_hz</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.002277777777777777</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1143556781431903</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0359258182303599</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>25.44231809901396</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.01922308719896011</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>22.50606950984227</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="J27" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.00773730892621249</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1896248615013074</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1973621704275199</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.1478910462254284</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.04173381527587905</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0.9599381198307105</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>0.06580089286454564</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>current_phase_a_skewness</t>
+          <t>current_phase_a_env_skew</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.001500000000000008</v>
+        <v>-0.00694444444444442</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1405067617283844</v>
+        <v>-0.6019636411144301</v>
       </c>
       <c r="D28" t="n">
-        <v>0.01576954494251258</v>
+        <v>0.02550782847608903</v>
       </c>
       <c r="E28" t="n">
-        <v>9.577914744189325</v>
+        <v>10.57540021437735</v>
       </c>
       <c r="F28" t="n">
-        <v>0.003839268421762652</v>
+        <v>0.009731914453223753</v>
       </c>
       <c r="G28" t="n">
-        <v>5.337310563153458</v>
+        <v>10.28071371809886</v>
       </c>
       <c r="H28" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="I28" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K28" t="n">
-        <v>0.005095301000188741</v>
+        <v>-0.02260397830018075</v>
       </c>
       <c r="L28" t="n">
-        <v>0.03787220726868831</v>
+        <v>0.09985215569158684</v>
       </c>
       <c r="M28" t="n">
-        <v>0.03277690626849957</v>
+        <v>0.1224561339917676</v>
       </c>
       <c r="N28" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="O28" t="n">
         <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>0.06491639202461487</v>
+        <v>0.1075024832226562</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.02704418475592656</v>
+        <v>0.007650327531069381</v>
       </c>
       <c r="R28" t="n">
-        <v>0.3303552703445691</v>
+        <v>0.332485459112823</v>
       </c>
       <c r="S28" t="n">
-        <v>0.0475448393931267</v>
+        <v>0.04969572269613522</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>current_phase_a_env_skew</t>
+          <t>current_phase_a_env_peak_sp_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.006999999999999992</v>
+        <v>0.002611111111111127</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.6162561171455492</v>
+        <v>0.224610393132413</v>
       </c>
       <c r="D29" t="n">
-        <v>0.02154247949491133</v>
+        <v>0.01204040074683335</v>
       </c>
       <c r="E29" t="n">
-        <v>9.497712338756237</v>
+        <v>7.146469267328671</v>
       </c>
       <c r="F29" t="n">
-        <v>0.008639579564466444</v>
+        <v>0.003633368029839157</v>
       </c>
       <c r="G29" t="n">
-        <v>5.25913341601094</v>
+        <v>2.614688926121446</v>
       </c>
       <c r="H29" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.02377807133421397</v>
+        <v>0.008499095840868044</v>
       </c>
       <c r="L29" t="n">
-        <v>0.08522455635690504</v>
+        <v>0.03727936902282923</v>
       </c>
       <c r="M29" t="n">
-        <v>0.109002627691119</v>
+        <v>0.02878027318196119</v>
       </c>
       <c r="N29" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="O29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P29" t="n">
-        <v>0.08868106525406641</v>
+        <v>0.05074414627234346</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.00345650889716137</v>
+        <v>0.01346477724951423</v>
       </c>
       <c r="R29" t="n">
-        <v>0.1998618351577149</v>
+        <v>0.4966563166632823</v>
       </c>
       <c r="S29" t="n">
-        <v>0.04737315247136235</v>
+        <v>0.04342392380913654</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>current_phase_a_env_centroid</t>
+          <t>current_phase_a_current_phase_b_env_energy_imbalance</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.007444444444444446</v>
+        <v>0.006555555555555559</v>
       </c>
       <c r="C30" t="n">
-        <v>-1.104310622563552</v>
+        <v>2.478850940509602</v>
       </c>
       <c r="D30" t="n">
-        <v>0.02210584619822572</v>
+        <v>0.01667625731717882</v>
       </c>
       <c r="E30" t="n">
-        <v>8.332768279170878</v>
+        <v>9.436037318644747</v>
       </c>
       <c r="F30" t="n">
-        <v>0.008136484908306417</v>
+        <v>0.003551867586355196</v>
       </c>
       <c r="G30" t="n">
-        <v>5.735436488139642</v>
+        <v>4.047877722135938</v>
       </c>
       <c r="H30" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="J30" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.02528779014908474</v>
+        <v>0.02133815551537072</v>
       </c>
       <c r="L30" t="n">
-        <v>0.08026181267744269</v>
+        <v>0.03644315174915621</v>
       </c>
       <c r="M30" t="n">
-        <v>0.1055496028265274</v>
+        <v>0.01510499623378549</v>
       </c>
       <c r="N30" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="O30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P30" t="n">
-        <v>0.09100020216634212</v>
+        <v>0.07028191655503811</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.01073838948889944</v>
+        <v>0.0338387648058819</v>
       </c>
       <c r="R30" t="n">
-        <v>0.4973297397749419</v>
+        <v>0.1986555483245722</v>
       </c>
       <c r="S30" t="n">
-        <v>0.04523750904036038</v>
+        <v>0.0384392067664063</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>frequency_hz</t>
+          <t>current_phase_a_env_dom_rel_peak_power</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>-0.009166666666666646</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>-0.8328441107691504</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.02641671696274452</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>7.953585538376921</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.0116655574333284</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>7.203731726428146</v>
       </c>
       <c r="H31" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="I31" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="J31" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>-0.02983725135623863</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>0.1196918717956875</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>0.1495291231519261</v>
       </c>
       <c r="N31" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>0.1113329844893375</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>0.008358887306349996</v>
       </c>
       <c r="R31" t="n">
-        <v>1</v>
+        <v>0.4979189756972268</v>
       </c>
       <c r="S31" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.03683305133816277</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>current_phase_a_env_peak_sp_mean</t>
+          <t>current_phase_a_env_fundamental_power_ratio</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.002222222222222209</v>
+        <v>-0.007944444444444424</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2404666990824222</v>
+        <v>-0.5778257033116704</v>
       </c>
       <c r="D32" t="n">
-        <v>0.01099119004952063</v>
+        <v>0.03133070637219805</v>
       </c>
       <c r="E32" t="n">
-        <v>3.47115910489493</v>
+        <v>11.06352322376441</v>
       </c>
       <c r="F32" t="n">
-        <v>0.00358486824885952</v>
+        <v>0.01258721152042395</v>
       </c>
       <c r="G32" t="n">
-        <v>3.298225016272395</v>
+        <v>4.878771597230229</v>
       </c>
       <c r="H32" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="I32" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="J32" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K32" t="n">
-        <v>0.007548594074353606</v>
+        <v>-0.02585895117540681</v>
       </c>
       <c r="L32" t="n">
-        <v>0.03536269373148317</v>
+        <v>0.1291482997000622</v>
       </c>
       <c r="M32" t="n">
-        <v>0.02781409965712957</v>
+        <v>0.155007250875469</v>
       </c>
       <c r="N32" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0.04524597283388972</v>
+        <v>0.1320429427886605</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.00988327910240655</v>
+        <v>0.002894643088598325</v>
       </c>
       <c r="R32" t="n">
-        <v>0.4975413300848943</v>
+        <v>0.9971137116859218</v>
       </c>
       <c r="S32" t="n">
-        <v>0.04161843419681983</v>
+        <v>0.0368256208058188</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>current_phase_a_current_phase_b_env_crest_diff</t>
+          <t>current_phase_a_env_thd_power_frac</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.007333333333333329</v>
+        <v>-0.008055555555555531</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.7938844752427617</v>
+        <v>-0.5427625338093259</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0221981026287617</v>
+        <v>0.04158053645107616</v>
       </c>
       <c r="E33" t="n">
-        <v>8.536792630741971</v>
+        <v>13.09994392366941</v>
       </c>
       <c r="F33" t="n">
-        <v>0.009014154258152638</v>
+        <v>0.0240012709380493</v>
       </c>
       <c r="G33" t="n">
-        <v>3.043595731214542</v>
+        <v>7.404949745977457</v>
       </c>
       <c r="H33" t="n">
         <v>31</v>
       </c>
       <c r="I33" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J33" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.02491036044536703</v>
+        <v>-0.02622061482820968</v>
       </c>
       <c r="L33" t="n">
-        <v>0.08891952343877843</v>
+        <v>0.2462597317332744</v>
       </c>
       <c r="M33" t="n">
-        <v>0.1138298838841455</v>
+        <v>0.2724803465614841</v>
       </c>
       <c r="N33" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.09137998196552455</v>
+        <v>0.1752407472243682</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.002460458526746118</v>
+        <v>0.07101898450890615</v>
       </c>
       <c r="R33" t="n">
-        <v>0.249846315875432</v>
+        <v>0.9336902654984491</v>
       </c>
       <c r="S33" t="n">
-        <v>0.04146997821645595</v>
+        <v>0.03416177885033463</v>
       </c>
     </row>
   </sheetData>
@@ -2668,13 +2668,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1013742978993689</v>
+        <v>0.09746323838298192</v>
       </c>
       <c r="D2" t="n">
-        <v>11.68422402249553</v>
+        <v>26.26616581547045</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01187668423282012</v>
+        <v>0.01169879519177517</v>
       </c>
       <c r="F2" t="n">
         <v>32</v>
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9784174698663071</v>
+        <v>0.959051558011515</v>
       </c>
     </row>
     <row r="7">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-11-04 17:54:52</t>
+          <t>2025-11-06 19:20:04</t>
         </is>
       </c>
     </row>
